--- a/DAT進捗コスト表.xlsx
+++ b/DAT進捗コスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiranoShinya\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AsoHiroto\Desktop\github\http_team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74F956A-143F-4D7D-B51C-8545C7D8D6DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B928EE-F1D1-47B3-A7F8-C3A433A1F70F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="アルファ" sheetId="1" r:id="rId1"/>
@@ -1023,8 +1023,8 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1393,8 +1393,8 @@
         <v>6</v>
       </c>
       <c r="J4">
-        <f>SUMIF(G3:G90,"完了",E3:E90)</f>
-        <v>36</v>
+        <f>SUMIF(G3:G114,"完了",E3:E114)</f>
+        <v>38</v>
       </c>
       <c r="M4" t="s">
         <v>7</v>
@@ -1422,22 +1422,22 @@
       </c>
       <c r="J5" s="2">
         <f ca="1">NETWORKDAYS(J6,J7)</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K5" t="s">
         <v>11</v>
       </c>
       <c r="L5" s="3">
         <f ca="1" xml:space="preserve"> J4 / J5</f>
-        <v>1.6363636363636365</v>
+        <v>1.5833333333333333</v>
       </c>
       <c r="M5" s="2">
         <f ca="1">_xlfn.DAYS(J7,J6)</f>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="N5" s="3">
         <f ca="1">J4/M5</f>
-        <v>1.2413793103448276</v>
+        <v>1.1515151515151516</v>
       </c>
       <c r="U5" t="s">
         <v>117</v>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="J7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46182</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1590,19 +1590,19 @@
       </c>
       <c r="K14" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),J14)</f>
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L14" s="3">
         <f ca="1">($J$2 - $J$4) / K14</f>
-        <v>4.1891891891891895</v>
+        <v>4.371428571428571</v>
       </c>
       <c r="M14">
         <f ca="1">_xlfn.DAYS(J14,$J$7)</f>
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="N14" s="3">
         <f ca="1">($J$2 - $J$4) / M14</f>
-        <v>2.9807692307692308</v>
+        <v>3.1875</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1625,19 +1625,19 @@
       </c>
       <c r="K15" s="2">
         <f t="shared" ref="K15:K16" ca="1" si="0">NETWORKDAYS(TODAY(),J15)</f>
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L15" s="3">
         <f ca="1">($J$2 - $J$4) / K15</f>
-        <v>3.7804878048780486</v>
+        <v>3.9230769230769229</v>
       </c>
       <c r="M15">
         <f ca="1">_xlfn.DAYS(J15,$J$7)</f>
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="N15" s="3">
         <f ca="1">($J$2 - $J$4) / M15</f>
-        <v>2.7678571428571428</v>
+        <v>2.9423076923076925</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1660,19 +1660,19 @@
       </c>
       <c r="K16" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L16" s="3">
         <f ca="1">($J$2 - $J$4) / K16</f>
-        <v>3.7804878048780486</v>
+        <v>3.9230769230769229</v>
       </c>
       <c r="M16">
         <f ca="1">_xlfn.DAYS(J16,$J$7)</f>
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="N16" s="3">
         <f ca="1">($J$2 - $J$4) / M16</f>
-        <v>2.7678571428571428</v>
+        <v>2.9423076923076925</v>
       </c>
     </row>
     <row r="17" spans="2:7">
@@ -3486,15 +3486,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
@@ -3550,6 +3541,15 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAF2F9FC-3A71-42D2-842A-D0923E27A331}">
   <ds:schemaRefs>
@@ -3570,14 +3570,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -3586,4 +3578,12 @@
     <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/DAT進捗コスト表.xlsx
+++ b/DAT進捗コスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiranoShinya\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FukudaGenki\Documents\GitHub\http_team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B74F956A-143F-4D7D-B51C-8545C7D8D6DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{402BD2FB-ACF3-4899-9DD8-9747FE763D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="アルファ" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1023,8 +1021,8 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1422,22 +1420,22 @@
       </c>
       <c r="J5" s="2">
         <f ca="1">NETWORKDAYS(J6,J7)</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K5" t="s">
         <v>11</v>
       </c>
       <c r="L5" s="3">
         <f ca="1" xml:space="preserve"> J4 / J5</f>
-        <v>1.6363636363636365</v>
+        <v>1.5</v>
       </c>
       <c r="M5" s="2">
         <f ca="1">_xlfn.DAYS(J7,J6)</f>
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="N5" s="3">
         <f ca="1">J4/M5</f>
-        <v>1.2413793103448276</v>
+        <v>1.0909090909090908</v>
       </c>
       <c r="U5" t="s">
         <v>117</v>
@@ -1481,7 +1479,7 @@
       </c>
       <c r="J7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46178</v>
+        <v>46182</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1590,19 +1588,19 @@
       </c>
       <c r="K14" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),J14)</f>
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L14" s="3">
-        <f ca="1">($J$2 - $J$4) / K14</f>
-        <v>4.1891891891891895</v>
+        <f ca="1">($J$3 - $J$4) / K14</f>
+        <v>0.33571428571428569</v>
       </c>
       <c r="M14">
         <f ca="1">_xlfn.DAYS(J14,$J$7)</f>
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="N14" s="3">
-        <f ca="1">($J$2 - $J$4) / M14</f>
-        <v>2.9807692307692308</v>
+        <f ca="1">($J$3 - $J$4) / M14</f>
+        <v>0.24479166666666666</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1625,19 +1623,19 @@
       </c>
       <c r="K15" s="2">
         <f t="shared" ref="K15:K16" ca="1" si="0">NETWORKDAYS(TODAY(),J15)</f>
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L15" s="3">
-        <f ca="1">($J$2 - $J$4) / K15</f>
-        <v>3.7804878048780486</v>
+        <f ca="1">($J$3 - $J$4) / K15</f>
+        <v>0.30128205128205127</v>
       </c>
       <c r="M15">
         <f ca="1">_xlfn.DAYS(J15,$J$7)</f>
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="N15" s="3">
-        <f ca="1">($J$2 - $J$4) / M15</f>
-        <v>2.7678571428571428</v>
+        <f ca="1">($J$3 - $J$4) / M15</f>
+        <v>0.22596153846153846</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1660,19 +1658,19 @@
       </c>
       <c r="K16" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L16" s="3">
-        <f ca="1">($J$2 - $J$4) / K16</f>
-        <v>3.7804878048780486</v>
+        <f ca="1">($J$3 - $J$4) / K16</f>
+        <v>0.30128205128205127</v>
       </c>
       <c r="M16">
         <f ca="1">_xlfn.DAYS(J16,$J$7)</f>
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="N16" s="3">
-        <f ca="1">($J$2 - $J$4) / M16</f>
-        <v>2.7678571428571428</v>
+        <f ca="1">($J$3 - $J$4) / M16</f>
+        <v>0.22596153846153846</v>
       </c>
     </row>
     <row r="17" spans="2:7">
@@ -3097,6 +3095,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100916D42E3690EEE418172DBF4B6395129" ma:contentTypeVersion="32" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="2bec52062c397840dce5bfa38caf7040">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c7208212-5067-493a-8683-cc3386cb0efe" xmlns:ns3="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="662986cd6941c04829d5352220b24469" ns2:_="" ns3:_="">
     <xsd:import namespace="c7208212-5067-493a-8683-cc3386cb0efe"/>
@@ -3485,15 +3492,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3551,6 +3549,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAF2F9FC-3A71-42D2-842A-D0923E27A331}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3569,14 +3575,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
   <ds:schemaRefs>

--- a/DAT進捗コスト表.xlsx
+++ b/DAT進捗コスト表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FukudaGenki\Documents\GitHub\http_team\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AsoHiroto\Desktop\github\http_team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{402BD2FB-ACF3-4899-9DD8-9747FE763D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CECA5C7C-A78D-4E49-82D4-1F31F78BAF54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="J4">
         <f>SUMIF(G3:G90,"完了",E3:E90)</f>
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="M4" t="s">
         <v>7</v>
@@ -1420,22 +1420,22 @@
       </c>
       <c r="J5" s="2">
         <f ca="1">NETWORKDAYS(J6,J7)</f>
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K5" t="s">
         <v>11</v>
       </c>
       <c r="L5" s="3">
         <f ca="1" xml:space="preserve"> J4 / J5</f>
-        <v>1.5</v>
+        <v>2.6206896551724137</v>
       </c>
       <c r="M5" s="2">
         <f ca="1">_xlfn.DAYS(J7,J6)</f>
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="N5" s="3">
         <f ca="1">J4/M5</f>
-        <v>1.0909090909090908</v>
+        <v>1.9</v>
       </c>
       <c r="U5" t="s">
         <v>117</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="J7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46182</v>
+        <v>46189</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1588,19 +1588,19 @@
       </c>
       <c r="K14" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),J14)</f>
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L14" s="3">
         <f ca="1">($J$3 - $J$4) / K14</f>
-        <v>0.33571428571428569</v>
+        <v>-0.94166666666666665</v>
       </c>
       <c r="M14">
         <f ca="1">_xlfn.DAYS(J14,$J$7)</f>
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="N14" s="3">
         <f ca="1">($J$3 - $J$4) / M14</f>
-        <v>0.24479166666666666</v>
+        <v>-0.68902439024390238</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1623,19 +1623,19 @@
       </c>
       <c r="K15" s="2">
         <f t="shared" ref="K15:K16" ca="1" si="0">NETWORKDAYS(TODAY(),J15)</f>
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="L15" s="3">
         <f ca="1">($J$3 - $J$4) / K15</f>
-        <v>0.30128205128205127</v>
+        <v>-0.83088235294117652</v>
       </c>
       <c r="M15">
         <f ca="1">_xlfn.DAYS(J15,$J$7)</f>
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="N15" s="3">
         <f ca="1">($J$3 - $J$4) / M15</f>
-        <v>0.22596153846153846</v>
+        <v>-0.62777777777777777</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1658,19 +1658,19 @@
       </c>
       <c r="K16" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="L16" s="3">
         <f ca="1">($J$3 - $J$4) / K16</f>
-        <v>0.30128205128205127</v>
+        <v>-0.83088235294117652</v>
       </c>
       <c r="M16">
         <f ca="1">_xlfn.DAYS(J16,$J$7)</f>
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="N16" s="3">
         <f ca="1">($J$3 - $J$4) / M16</f>
-        <v>0.22596153846153846</v>
+        <v>-0.62777777777777777</v>
       </c>
     </row>
     <row r="17" spans="2:7">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="F81" s="12"/>
       <c r="G81" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82" spans="2:7">
@@ -2560,7 +2560,7 @@
       </c>
       <c r="F82" s="12"/>
       <c r="G82" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83" spans="2:7">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="F83" s="12"/>
       <c r="G83" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84" spans="2:7">
@@ -3104,6 +3104,62 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Teachers>
+    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Students>
+    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Student_Groups>
+    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100916D42E3690EEE418172DBF4B6395129" ma:contentTypeVersion="32" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="2bec52062c397840dce5bfa38caf7040">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c7208212-5067-493a-8683-cc3386cb0efe" xmlns:ns3="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="662986cd6941c04829d5352220b24469" ns2:_="" ns3:_="">
     <xsd:import namespace="c7208212-5067-493a-8683-cc3386cb0efe"/>
@@ -3492,62 +3548,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Teachers>
-    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Students>
-    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Student_Groups>
-    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
   <ds:schemaRefs>
@@ -3557,6 +3557,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
+    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAF2F9FC-3A71-42D2-842A-D0923E27A331}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3573,15 +3584,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
-    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/DAT進捗コスト表.xlsx
+++ b/DAT進捗コスト表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AsoHiroto\Desktop\github\http_team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CECA5C7C-A78D-4E49-82D4-1F31F78BAF54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A17D6A-A317-4740-BF83-63E4168F2289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="J4">
         <f>SUMIF(G3:G90,"完了",E3:E90)</f>
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M4" t="s">
         <v>7</v>
@@ -1420,22 +1420,22 @@
       </c>
       <c r="J5" s="2">
         <f ca="1">NETWORKDAYS(J6,J7)</f>
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="K5" t="s">
         <v>11</v>
       </c>
       <c r="L5" s="3">
         <f ca="1" xml:space="preserve"> J4 / J5</f>
-        <v>2.6206896551724137</v>
+        <v>2</v>
       </c>
       <c r="M5" s="2">
         <f ca="1">_xlfn.DAYS(J7,J6)</f>
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="N5" s="3">
         <f ca="1">J4/M5</f>
-        <v>1.9</v>
+        <v>1.4444444444444444</v>
       </c>
       <c r="U5" t="s">
         <v>117</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="J7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1588,19 +1588,19 @@
       </c>
       <c r="K14" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),J14)</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L14" s="3">
         <f ca="1">($J$3 - $J$4) / K14</f>
-        <v>-0.94166666666666665</v>
+        <v>-1.5125</v>
       </c>
       <c r="M14">
         <f ca="1">_xlfn.DAYS(J14,$J$7)</f>
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="N14" s="3">
         <f ca="1">($J$3 - $J$4) / M14</f>
-        <v>-0.68902439024390238</v>
+        <v>-1.1203703703703705</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1623,19 +1623,19 @@
       </c>
       <c r="K15" s="2">
         <f t="shared" ref="K15:K16" ca="1" si="0">NETWORKDAYS(TODAY(),J15)</f>
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="L15" s="3">
         <f ca="1">($J$3 - $J$4) / K15</f>
-        <v>-0.83088235294117652</v>
+        <v>-1.2604166666666667</v>
       </c>
       <c r="M15">
         <f ca="1">_xlfn.DAYS(J15,$J$7)</f>
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="N15" s="3">
         <f ca="1">($J$3 - $J$4) / M15</f>
-        <v>-0.62777777777777777</v>
+        <v>-0.97580645161290325</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1658,19 +1658,19 @@
       </c>
       <c r="K16" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="L16" s="3">
         <f ca="1">($J$3 - $J$4) / K16</f>
-        <v>-0.83088235294117652</v>
+        <v>-1.2604166666666667</v>
       </c>
       <c r="M16">
         <f ca="1">_xlfn.DAYS(J16,$J$7)</f>
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="N16" s="3">
         <f ca="1">($J$3 - $J$4) / M16</f>
-        <v>-0.62777777777777777</v>
+        <v>-0.97580645161290325</v>
       </c>
     </row>
     <row r="17" spans="2:7">
@@ -2532,7 +2532,7 @@
       <c r="E80" s="16"/>
       <c r="F80" s="16"/>
       <c r="G80" s="16" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81" spans="2:7">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="F90" s="12"/>
       <c r="G90" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="91" spans="2:7">
@@ -3104,62 +3104,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Teachers>
-    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Students>
-    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Student_Groups>
-    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100916D42E3690EEE418172DBF4B6395129" ma:contentTypeVersion="32" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="2bec52062c397840dce5bfa38caf7040">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c7208212-5067-493a-8683-cc3386cb0efe" xmlns:ns3="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="662986cd6941c04829d5352220b24469" ns2:_="" ns3:_="">
     <xsd:import namespace="c7208212-5067-493a-8683-cc3386cb0efe"/>
@@ -3548,6 +3492,62 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Teachers>
+    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Students>
+    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Student_Groups>
+    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
   <ds:schemaRefs>
@@ -3557,17 +3557,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
-    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAF2F9FC-3A71-42D2-842A-D0923E27A331}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3584,4 +3573,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
+    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/DAT進捗コスト表.xlsx
+++ b/DAT進捗コスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AsoHiroto\Desktop\github\http_team\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiranoShinya\Desktop\http_team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A17D6A-A317-4740-BF83-63E4168F2289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB1D4371-0C16-46D0-8ED8-E996FFE4E545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="アルファ" sheetId="1" r:id="rId1"/>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="J4">
         <f>SUMIF(G3:G90,"完了",E3:E90)</f>
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="M4" t="s">
         <v>7</v>
@@ -1420,22 +1420,22 @@
       </c>
       <c r="J5" s="2">
         <f ca="1">NETWORKDAYS(J6,J7)</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K5" t="s">
         <v>11</v>
       </c>
       <c r="L5" s="3">
         <f ca="1" xml:space="preserve"> J4 / J5</f>
-        <v>2</v>
+        <v>3.2749999999999999</v>
       </c>
       <c r="M5" s="2">
         <f ca="1">_xlfn.DAYS(J7,J6)</f>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N5" s="3">
         <f ca="1">J4/M5</f>
-        <v>1.4444444444444444</v>
+        <v>2.3818181818181818</v>
       </c>
       <c r="U5" t="s">
         <v>117</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="J7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1588,19 +1588,19 @@
       </c>
       <c r="K14" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),J14)</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L14" s="3">
         <f ca="1">($J$3 - $J$4) / K14</f>
-        <v>-1.5125</v>
+        <v>-4.3815789473684212</v>
       </c>
       <c r="M14">
         <f ca="1">_xlfn.DAYS(J14,$J$7)</f>
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N14" s="3">
         <f ca="1">($J$3 - $J$4) / M14</f>
-        <v>-1.1203703703703705</v>
+        <v>-3.2019230769230771</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1623,19 +1623,19 @@
       </c>
       <c r="K15" s="2">
         <f t="shared" ref="K15:K16" ca="1" si="0">NETWORKDAYS(TODAY(),J15)</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L15" s="3">
         <f ca="1">($J$3 - $J$4) / K15</f>
-        <v>-1.2604166666666667</v>
+        <v>-3.6195652173913042</v>
       </c>
       <c r="M15">
         <f ca="1">_xlfn.DAYS(J15,$J$7)</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N15" s="3">
         <f ca="1">($J$3 - $J$4) / M15</f>
-        <v>-0.97580645161290325</v>
+        <v>-2.7749999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1658,19 +1658,19 @@
       </c>
       <c r="K16" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L16" s="3">
         <f ca="1">($J$3 - $J$4) / K16</f>
-        <v>-1.2604166666666667</v>
+        <v>-3.6195652173913042</v>
       </c>
       <c r="M16">
         <f ca="1">_xlfn.DAYS(J16,$J$7)</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N16" s="3">
         <f ca="1">($J$3 - $J$4) / M16</f>
-        <v>-0.97580645161290325</v>
+        <v>-2.7749999999999999</v>
       </c>
     </row>
     <row r="17" spans="2:7">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="F30" s="12"/>
       <c r="G30" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="2:7">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="F31" s="12"/>
       <c r="G31" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="2:7">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="F32" s="12"/>
       <c r="G32" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="2:7">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="F33" s="12"/>
       <c r="G33" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="2:7">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="F34" s="12"/>
       <c r="G34" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="F35" s="12"/>
       <c r="G35" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="F36" s="12"/>
       <c r="G36" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="2:7">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="F37" s="12"/>
       <c r="G37" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="2:7">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F53" s="12"/>
       <c r="G53" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="2:7">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="F54" s="12"/>
       <c r="G54" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55" spans="2:7">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="F55" s="12"/>
       <c r="G55" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="2:7">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F56" s="12"/>
       <c r="G56" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="2:7">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="F57" s="12"/>
       <c r="G57" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58" spans="2:7">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="F58" s="12"/>
       <c r="G58" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" spans="2:7">
@@ -3104,6 +3104,62 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Teachers>
+    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Students>
+    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Student_Groups>
+    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100916D42E3690EEE418172DBF4B6395129" ma:contentTypeVersion="32" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="2bec52062c397840dce5bfa38caf7040">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c7208212-5067-493a-8683-cc3386cb0efe" xmlns:ns3="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="662986cd6941c04829d5352220b24469" ns2:_="" ns3:_="">
     <xsd:import namespace="c7208212-5067-493a-8683-cc3386cb0efe"/>
@@ -3492,62 +3548,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Teachers>
-    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Students>
-    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Student_Groups>
-    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
   <ds:schemaRefs>
@@ -3557,6 +3557,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
+    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAF2F9FC-3A71-42D2-842A-D0923E27A331}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3573,15 +3584,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
-    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/DAT進捗コスト表.xlsx
+++ b/DAT進捗コスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiranoShinya\Desktop\http_team\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TeraoAyato\Documents\GitHub\http_team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB1D4371-0C16-46D0-8ED8-E996FFE4E545}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34935473-C8AD-44A8-B0B0-0BD865686737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="アルファ" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="120">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
   </si>
@@ -863,6 +863,10 @@
     <rPh sb="0" eb="3">
       <t>カンスウヨウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>？</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1420,22 +1424,22 @@
       </c>
       <c r="J5" s="2">
         <f ca="1">NETWORKDAYS(J6,J7)</f>
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K5" t="s">
         <v>11</v>
       </c>
       <c r="L5" s="3">
         <f ca="1" xml:space="preserve"> J4 / J5</f>
-        <v>3.2749999999999999</v>
+        <v>3.0465116279069768</v>
       </c>
       <c r="M5" s="2">
         <f ca="1">_xlfn.DAYS(J7,J6)</f>
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="N5" s="3">
         <f ca="1">J4/M5</f>
-        <v>2.3818181818181818</v>
+        <v>2.1833333333333331</v>
       </c>
       <c r="U5" t="s">
         <v>117</v>
@@ -1479,7 +1483,7 @@
       </c>
       <c r="J7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46209</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1588,19 +1592,19 @@
       </c>
       <c r="K14" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),J14)</f>
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L14" s="3">
         <f ca="1">($J$3 - $J$4) / K14</f>
-        <v>-4.3815789473684212</v>
+        <v>-5.203125</v>
       </c>
       <c r="M14">
         <f ca="1">_xlfn.DAYS(J14,$J$7)</f>
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N14" s="3">
         <f ca="1">($J$3 - $J$4) / M14</f>
-        <v>-3.2019230769230771</v>
+        <v>-3.9642857142857144</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1623,19 +1627,19 @@
       </c>
       <c r="K15" s="2">
         <f t="shared" ref="K15:K16" ca="1" si="0">NETWORKDAYS(TODAY(),J15)</f>
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L15" s="3">
         <f ca="1">($J$3 - $J$4) / K15</f>
-        <v>-3.6195652173913042</v>
+        <v>-4.1624999999999996</v>
       </c>
       <c r="M15">
         <f ca="1">_xlfn.DAYS(J15,$J$7)</f>
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N15" s="3">
         <f ca="1">($J$3 - $J$4) / M15</f>
-        <v>-2.7749999999999999</v>
+        <v>-3.33</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1658,19 +1662,19 @@
       </c>
       <c r="K16" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L16" s="3">
         <f ca="1">($J$3 - $J$4) / K16</f>
-        <v>-3.6195652173913042</v>
+        <v>-4.1624999999999996</v>
       </c>
       <c r="M16">
         <f ca="1">_xlfn.DAYS(J16,$J$7)</f>
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N16" s="3">
         <f ca="1">($J$3 - $J$4) / M16</f>
-        <v>-2.7749999999999999</v>
+        <v>-3.33</v>
       </c>
     </row>
     <row r="17" spans="2:7">
@@ -2726,7 +2730,7 @@
       </c>
       <c r="F94" s="12"/>
       <c r="G94" s="12" t="s">
-        <v>5</v>
+        <v>119</v>
       </c>
     </row>
     <row r="95" spans="2:7">
@@ -2740,7 +2744,7 @@
       </c>
       <c r="F95" s="12"/>
       <c r="G95" s="12" t="s">
-        <v>5</v>
+        <v>119</v>
       </c>
     </row>
     <row r="96" spans="2:7">
@@ -2896,7 +2900,7 @@
       </c>
       <c r="F108" s="12"/>
       <c r="G108" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="109" spans="2:7">
@@ -2910,7 +2914,7 @@
       </c>
       <c r="F109" s="12"/>
       <c r="G109" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="110" spans="2:7">
@@ -2924,7 +2928,7 @@
       </c>
       <c r="F110" s="12"/>
       <c r="G110" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="111" spans="2:7">
@@ -2938,7 +2942,7 @@
       </c>
       <c r="F111" s="12"/>
       <c r="G111" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="112" spans="2:7">
@@ -2952,7 +2956,7 @@
       </c>
       <c r="F112" s="12"/>
       <c r="G112" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="113" spans="2:7">
@@ -2966,7 +2970,7 @@
       </c>
       <c r="F113" s="12"/>
       <c r="G113" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="114" spans="2:7">
@@ -2980,7 +2984,7 @@
       </c>
       <c r="F114" s="12"/>
       <c r="G114" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="115" spans="2:7">
@@ -3104,62 +3108,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Teachers>
-    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Students>
-    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Student_Groups>
-    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100916D42E3690EEE418172DBF4B6395129" ma:contentTypeVersion="32" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="2bec52062c397840dce5bfa38caf7040">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c7208212-5067-493a-8683-cc3386cb0efe" xmlns:ns3="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="662986cd6941c04829d5352220b24469" ns2:_="" ns3:_="">
     <xsd:import namespace="c7208212-5067-493a-8683-cc3386cb0efe"/>
@@ -3548,6 +3496,62 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Teachers>
+    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Students>
+    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Student_Groups>
+    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
   <ds:schemaRefs>
@@ -3557,17 +3561,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
-    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAF2F9FC-3A71-42D2-842A-D0923E27A331}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3584,4 +3577,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
+    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/DAT進捗コスト表.xlsx
+++ b/DAT進捗コスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TeraoAyato\Documents\GitHub\http_team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34935473-C8AD-44A8-B0B0-0BD865686737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8139D487-0B29-4F62-8396-7DE23E813137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="J4">
         <f>SUMIF(G3:G90,"完了",E3:E90)</f>
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="M4" t="s">
         <v>7</v>
@@ -1424,22 +1424,22 @@
       </c>
       <c r="J5" s="2">
         <f ca="1">NETWORKDAYS(J6,J7)</f>
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K5" t="s">
         <v>11</v>
       </c>
       <c r="L5" s="3">
         <f ca="1" xml:space="preserve"> J4 / J5</f>
-        <v>3.0465116279069768</v>
+        <v>2.8913043478260869</v>
       </c>
       <c r="M5" s="2">
         <f ca="1">_xlfn.DAYS(J7,J6)</f>
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="N5" s="3">
         <f ca="1">J4/M5</f>
-        <v>2.1833333333333331</v>
+        <v>2.1111111111111112</v>
       </c>
       <c r="U5" t="s">
         <v>117</v>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="J7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46209</v>
+        <v>46212</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1592,19 +1592,19 @@
       </c>
       <c r="K14" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),J14)</f>
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="L14" s="3">
         <f ca="1">($J$3 - $J$4) / K14</f>
-        <v>-5.203125</v>
+        <v>-6.5576923076923075</v>
       </c>
       <c r="M14">
         <f ca="1">_xlfn.DAYS(J14,$J$7)</f>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="N14" s="3">
         <f ca="1">($J$3 - $J$4) / M14</f>
-        <v>-3.9642857142857144</v>
+        <v>-4.7361111111111107</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1627,19 +1627,19 @@
       </c>
       <c r="K15" s="2">
         <f t="shared" ref="K15:K16" ca="1" si="0">NETWORKDAYS(TODAY(),J15)</f>
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L15" s="3">
         <f ca="1">($J$3 - $J$4) / K15</f>
-        <v>-4.1624999999999996</v>
+        <v>-5.0147058823529411</v>
       </c>
       <c r="M15">
         <f ca="1">_xlfn.DAYS(J15,$J$7)</f>
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N15" s="3">
         <f ca="1">($J$3 - $J$4) / M15</f>
-        <v>-3.33</v>
+        <v>-3.875</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1662,19 +1662,19 @@
       </c>
       <c r="K16" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="L16" s="3">
         <f ca="1">($J$3 - $J$4) / K16</f>
-        <v>-4.1624999999999996</v>
+        <v>-5.0147058823529411</v>
       </c>
       <c r="M16">
         <f ca="1">_xlfn.DAYS(J16,$J$7)</f>
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N16" s="3">
         <f ca="1">($J$3 - $J$4) / M16</f>
-        <v>-3.33</v>
+        <v>-3.875</v>
       </c>
     </row>
     <row r="17" spans="2:7">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="F45" s="12"/>
       <c r="G45" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="2:7">
@@ -3108,6 +3108,62 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Teachers>
+    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Students>
+    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Student_Groups>
+    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100916D42E3690EEE418172DBF4B6395129" ma:contentTypeVersion="32" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="2bec52062c397840dce5bfa38caf7040">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c7208212-5067-493a-8683-cc3386cb0efe" xmlns:ns3="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="662986cd6941c04829d5352220b24469" ns2:_="" ns3:_="">
     <xsd:import namespace="c7208212-5067-493a-8683-cc3386cb0efe"/>
@@ -3496,62 +3552,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Teachers>
-    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Students>
-    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Student_Groups>
-    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
   <ds:schemaRefs>
@@ -3561,6 +3561,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
+    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAF2F9FC-3A71-42D2-842A-D0923E27A331}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3577,15 +3588,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
-    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/DAT進捗コスト表.xlsx
+++ b/DAT進捗コスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TeraoAyato\Documents\GitHub\http_team\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiranoShinya\Desktop\http_team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8139D487-0B29-4F62-8396-7DE23E813137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1AD607F-7F3C-471D-9F71-04ED47FEDBD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="アルファ" sheetId="1" r:id="rId1"/>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="J4">
         <f>SUMIF(G3:G90,"完了",E3:E90)</f>
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="M4" t="s">
         <v>7</v>
@@ -1424,22 +1424,22 @@
       </c>
       <c r="J5" s="2">
         <f ca="1">NETWORKDAYS(J6,J7)</f>
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K5" t="s">
         <v>11</v>
       </c>
       <c r="L5" s="3">
         <f ca="1" xml:space="preserve"> J4 / J5</f>
-        <v>2.8913043478260869</v>
+        <v>2.8367346938775508</v>
       </c>
       <c r="M5" s="2">
         <f ca="1">_xlfn.DAYS(J7,J6)</f>
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="N5" s="3">
         <f ca="1">J4/M5</f>
-        <v>2.1111111111111112</v>
+        <v>2.0441176470588234</v>
       </c>
       <c r="U5" t="s">
         <v>117</v>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="J7" s="1">
         <f ca="1">TODAY()</f>
-        <v>46212</v>
+        <v>46217</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -1592,19 +1592,19 @@
       </c>
       <c r="K14" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),J14)</f>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L14" s="3">
         <f ca="1">($J$3 - $J$4) / K14</f>
-        <v>-6.5576923076923075</v>
+        <v>-9.125</v>
       </c>
       <c r="M14">
         <f ca="1">_xlfn.DAYS(J14,$J$7)</f>
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="N14" s="3">
         <f ca="1">($J$3 - $J$4) / M14</f>
-        <v>-4.7361111111111107</v>
+        <v>-7.0192307692307692</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -1627,19 +1627,19 @@
       </c>
       <c r="K15" s="2">
         <f t="shared" ref="K15:K16" ca="1" si="0">NETWORKDAYS(TODAY(),J15)</f>
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L15" s="3">
         <f ca="1">($J$3 - $J$4) / K15</f>
-        <v>-5.0147058823529411</v>
+        <v>-6.5178571428571432</v>
       </c>
       <c r="M15">
         <f ca="1">_xlfn.DAYS(J15,$J$7)</f>
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N15" s="3">
         <f ca="1">($J$3 - $J$4) / M15</f>
-        <v>-3.875</v>
+        <v>-5.367647058823529</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -1662,19 +1662,19 @@
       </c>
       <c r="K16" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L16" s="3">
         <f ca="1">($J$3 - $J$4) / K16</f>
-        <v>-5.0147058823529411</v>
+        <v>-6.5178571428571432</v>
       </c>
       <c r="M16">
         <f ca="1">_xlfn.DAYS(J16,$J$7)</f>
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N16" s="3">
         <f ca="1">($J$3 - $J$4) / M16</f>
-        <v>-3.875</v>
+        <v>-5.367647058823529</v>
       </c>
     </row>
     <row r="17" spans="2:7">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="F50" s="12"/>
       <c r="G50" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="2:7">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="F51" s="12"/>
       <c r="G51" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="2:7">
@@ -3108,62 +3108,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Teachers>
-    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Students>
-    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Student_Groups>
-    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100916D42E3690EEE418172DBF4B6395129" ma:contentTypeVersion="32" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="2bec52062c397840dce5bfa38caf7040">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c7208212-5067-493a-8683-cc3386cb0efe" xmlns:ns3="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="662986cd6941c04829d5352220b24469" ns2:_="" ns3:_="">
     <xsd:import namespace="c7208212-5067-493a-8683-cc3386cb0efe"/>
@@ -3552,6 +3496,62 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Teachers>
+    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Students>
+    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Student_Groups>
+    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
   <ds:schemaRefs>
@@ -3561,17 +3561,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
-    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAF2F9FC-3A71-42D2-842A-D0923E27A331}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3588,4 +3577,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
+    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/DAT進捗コスト表.xlsx
+++ b/DAT進捗コスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HiranoShinya\Desktop\http_team\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1AD607F-7F3C-471D-9F71-04ED47FEDBD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F093F221-91B8-4A02-9B2B-C58715FBCE78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="116">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
   </si>
@@ -731,10 +731,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ストア</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>寺尾</t>
     <rPh sb="0" eb="2">
       <t>テラオ</t>
@@ -742,14 +738,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>　ー　パック</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　ー　UI</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・手札</t>
     <rPh sb="1" eb="3">
       <t>テフダ</t>
@@ -863,10 +851,6 @@
     <rPh sb="0" eb="3">
       <t>カンスウヨウ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>？</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1310,7 +1294,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V127"/>
+  <dimension ref="A1:V124"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="3" max="3" width="37.75" bestFit="1" customWidth="1"/>
@@ -1338,7 +1322,7 @@
         <v>22</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E2" s="13" t="s">
         <v>1</v>
@@ -1373,7 +1357,7 @@
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="I3" s="16" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="J3">
         <f>J2/V5</f>
@@ -1405,7 +1389,7 @@
         <v>8</v>
       </c>
       <c r="U4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -1442,7 +1426,7 @@
         <v>2.0441176470588234</v>
       </c>
       <c r="U5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="V5">
         <v>4</v>
@@ -1743,7 +1727,7 @@
         <v>78</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E22" s="16"/>
       <c r="F22" s="16"/>
@@ -1757,7 +1741,7 @@
         <v>77</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E23" s="15"/>
       <c r="F23" s="15"/>
@@ -1829,7 +1813,7 @@
         <v>44</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
@@ -2049,7 +2033,7 @@
         <v>76</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E45" s="12">
         <v>2</v>
@@ -2109,7 +2093,7 @@
         <v>69</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E49" s="16"/>
       <c r="F49" s="16"/>
@@ -2151,7 +2135,7 @@
         <v>73</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E52" s="16"/>
       <c r="F52" s="16"/>
@@ -2249,7 +2233,7 @@
         <v>74</v>
       </c>
       <c r="D59" s="16" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E59" s="16"/>
       <c r="F59" s="16"/>
@@ -2347,7 +2331,7 @@
         <v>75</v>
       </c>
       <c r="D66" s="16" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E66" s="16"/>
       <c r="F66" s="16"/>
@@ -2531,7 +2515,7 @@
         <v>92</v>
       </c>
       <c r="D80" s="16" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E80" s="16"/>
       <c r="F80" s="16"/>
@@ -2639,7 +2623,7 @@
         <v>85</v>
       </c>
       <c r="D88" s="16" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E88" s="12">
         <v>2</v>
@@ -2655,7 +2639,7 @@
         <v>86</v>
       </c>
       <c r="D89" s="16" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E89" s="12">
         <v>5</v>
@@ -2671,7 +2655,7 @@
         <v>87</v>
       </c>
       <c r="D90" s="16" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E90" s="12">
         <v>2</v>
@@ -2687,7 +2671,7 @@
         <v>88</v>
       </c>
       <c r="D91" s="16" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E91" s="12">
         <v>2</v>
@@ -2706,45 +2690,35 @@
       <c r="G92" s="12"/>
     </row>
     <row r="93" spans="2:7">
-      <c r="B93" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="C93" s="16" t="s">
+      <c r="B93" s="12"/>
+      <c r="C93" s="12"/>
+      <c r="D93" s="12"/>
+      <c r="E93" s="12"/>
+      <c r="F93" s="12"/>
+      <c r="G93" s="12"/>
+    </row>
+    <row r="94" spans="2:7">
+      <c r="B94" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D93" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="E93" s="16"/>
-      <c r="F93" s="16"/>
-      <c r="G93" s="16"/>
-    </row>
-    <row r="94" spans="2:7">
-      <c r="B94" s="12"/>
-      <c r="C94" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="D94" s="12"/>
-      <c r="E94" s="12">
-        <v>8</v>
-      </c>
-      <c r="F94" s="12"/>
-      <c r="G94" s="12" t="s">
-        <v>119</v>
-      </c>
+      <c r="C94" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D94" s="4"/>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
+      <c r="G94" s="4"/>
     </row>
     <row r="95" spans="2:7">
       <c r="B95" s="12"/>
       <c r="C95" s="12" t="s">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="D95" s="12"/>
-      <c r="E95" s="12">
-        <v>8</v>
-      </c>
+      <c r="E95" s="12"/>
       <c r="F95" s="12"/>
       <c r="G95" s="12" t="s">
-        <v>119</v>
+        <v>9</v>
       </c>
     </row>
     <row r="96" spans="2:7">
@@ -2756,21 +2730,25 @@
       <c r="G96" s="12"/>
     </row>
     <row r="97" spans="2:7">
-      <c r="B97" s="4" t="s">
-        <v>98</v>
-      </c>
+      <c r="B97" s="4"/>
       <c r="C97" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D97" s="4"/>
-      <c r="E97" s="4"/>
+        <v>96</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E97" s="4">
+        <v>34</v>
+      </c>
       <c r="F97" s="4"/>
       <c r="G97" s="4"/>
     </row>
     <row r="98" spans="2:7">
-      <c r="B98" s="12"/>
+      <c r="B98" s="12" t="s">
+        <v>64</v>
+      </c>
       <c r="C98" s="12" t="s">
-        <v>18</v>
+        <v>98</v>
       </c>
       <c r="D98" s="12"/>
       <c r="E98" s="12"/>
@@ -2781,29 +2759,31 @@
     </row>
     <row r="99" spans="2:7">
       <c r="B99" s="12"/>
-      <c r="C99" s="12"/>
+      <c r="C99" s="12" t="s">
+        <v>99</v>
+      </c>
       <c r="D99" s="12"/>
       <c r="E99" s="12"/>
       <c r="F99" s="12"/>
-      <c r="G99" s="12"/>
+      <c r="G99" s="12" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="100" spans="2:7">
-      <c r="B100" s="4"/>
-      <c r="C100" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D100" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E100" s="4">
-        <v>34</v>
-      </c>
-      <c r="F100" s="4"/>
-      <c r="G100" s="4"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D100" s="12"/>
+      <c r="E100" s="12"/>
+      <c r="F100" s="12"/>
+      <c r="G100" s="12" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="101" spans="2:7">
       <c r="B101" s="12" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="C101" s="12" t="s">
         <v>101</v>
@@ -2816,7 +2796,9 @@
       </c>
     </row>
     <row r="102" spans="2:7">
-      <c r="B102" s="12"/>
+      <c r="B102" s="12" t="s">
+        <v>97</v>
+      </c>
       <c r="C102" s="12" t="s">
         <v>102</v>
       </c>
@@ -2829,39 +2811,35 @@
     </row>
     <row r="103" spans="2:7">
       <c r="B103" s="12"/>
-      <c r="C103" s="12" t="s">
-        <v>103</v>
-      </c>
+      <c r="C103" s="12"/>
       <c r="D103" s="12"/>
       <c r="E103" s="12"/>
       <c r="F103" s="12"/>
-      <c r="G103" s="12" t="s">
-        <v>9</v>
-      </c>
+      <c r="G103" s="12"/>
     </row>
     <row r="104" spans="2:7">
-      <c r="B104" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="C104" s="12" t="s">
+      <c r="B104" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="C104" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="D104" s="12"/>
-      <c r="E104" s="12"/>
-      <c r="F104" s="12"/>
-      <c r="G104" s="12" t="s">
-        <v>9</v>
-      </c>
+      <c r="D104" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E104" s="16"/>
+      <c r="F104" s="16"/>
+      <c r="G104" s="16"/>
     </row>
     <row r="105" spans="2:7">
-      <c r="B105" s="12" t="s">
-        <v>98</v>
-      </c>
+      <c r="B105" s="12"/>
       <c r="C105" s="12" t="s">
         <v>105</v>
       </c>
       <c r="D105" s="12"/>
-      <c r="E105" s="12"/>
+      <c r="E105" s="12">
+        <v>6</v>
+      </c>
       <c r="F105" s="12"/>
       <c r="G105" s="12" t="s">
         <v>9</v>
@@ -2869,25 +2847,31 @@
     </row>
     <row r="106" spans="2:7">
       <c r="B106" s="12"/>
-      <c r="C106" s="12"/>
+      <c r="C106" s="12" t="s">
+        <v>106</v>
+      </c>
       <c r="D106" s="12"/>
-      <c r="E106" s="12"/>
+      <c r="E106" s="12">
+        <v>2</v>
+      </c>
       <c r="F106" s="12"/>
-      <c r="G106" s="12"/>
+      <c r="G106" s="12" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="107" spans="2:7">
-      <c r="B107" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="C107" s="16" t="s">
+      <c r="B107" s="12"/>
+      <c r="C107" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="D107" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="E107" s="16"/>
-      <c r="F107" s="16"/>
-      <c r="G107" s="16"/>
+      <c r="D107" s="12"/>
+      <c r="E107" s="12">
+        <v>2</v>
+      </c>
+      <c r="F107" s="12"/>
+      <c r="G107" s="12" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="108" spans="2:7">
       <c r="B108" s="12"/>
@@ -2924,7 +2908,7 @@
       </c>
       <c r="D110" s="12"/>
       <c r="E110" s="12">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F110" s="12"/>
       <c r="G110" s="12" t="s">
@@ -2934,11 +2918,11 @@
     <row r="111" spans="2:7">
       <c r="B111" s="12"/>
       <c r="C111" s="12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D111" s="12"/>
       <c r="E111" s="12">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F111" s="12"/>
       <c r="G111" s="12" t="s">
@@ -2947,45 +2931,27 @@
     </row>
     <row r="112" spans="2:7">
       <c r="B112" s="12"/>
-      <c r="C112" s="12" t="s">
-        <v>112</v>
-      </c>
+      <c r="C112" s="12"/>
       <c r="D112" s="12"/>
-      <c r="E112" s="12">
-        <v>2</v>
-      </c>
+      <c r="E112" s="12"/>
       <c r="F112" s="12"/>
-      <c r="G112" s="12" t="s">
-        <v>9</v>
-      </c>
+      <c r="G112" s="12"/>
     </row>
     <row r="113" spans="2:7">
       <c r="B113" s="12"/>
-      <c r="C113" s="12" t="s">
-        <v>113</v>
-      </c>
+      <c r="C113" s="12"/>
       <c r="D113" s="12"/>
-      <c r="E113" s="12">
-        <v>6</v>
-      </c>
+      <c r="E113" s="12"/>
       <c r="F113" s="12"/>
-      <c r="G113" s="12" t="s">
-        <v>9</v>
-      </c>
+      <c r="G113" s="12"/>
     </row>
     <row r="114" spans="2:7">
       <c r="B114" s="12"/>
-      <c r="C114" s="12" t="s">
-        <v>112</v>
-      </c>
+      <c r="C114" s="12"/>
       <c r="D114" s="12"/>
-      <c r="E114" s="12">
-        <v>2</v>
-      </c>
+      <c r="E114" s="12"/>
       <c r="F114" s="12"/>
-      <c r="G114" s="12" t="s">
-        <v>9</v>
-      </c>
+      <c r="G114" s="12"/>
     </row>
     <row r="115" spans="2:7">
       <c r="B115" s="12"/>
@@ -3066,30 +3032,6 @@
       <c r="E124" s="12"/>
       <c r="F124" s="12"/>
       <c r="G124" s="12"/>
-    </row>
-    <row r="125" spans="2:7">
-      <c r="B125" s="12"/>
-      <c r="C125" s="12"/>
-      <c r="D125" s="12"/>
-      <c r="E125" s="12"/>
-      <c r="F125" s="12"/>
-      <c r="G125" s="12"/>
-    </row>
-    <row r="126" spans="2:7">
-      <c r="B126" s="12"/>
-      <c r="C126" s="12"/>
-      <c r="D126" s="12"/>
-      <c r="E126" s="12"/>
-      <c r="F126" s="12"/>
-      <c r="G126" s="12"/>
-    </row>
-    <row r="127" spans="2:7">
-      <c r="B127" s="12"/>
-      <c r="C127" s="12"/>
-      <c r="D127" s="12"/>
-      <c r="E127" s="12"/>
-      <c r="F127" s="12"/>
-      <c r="G127" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -3108,6 +3050,62 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Owner>
+    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Teachers>
+    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Students>
+    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </Student_Groups>
+    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100916D42E3690EEE418172DBF4B6395129" ma:contentTypeVersion="32" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="2bec52062c397840dce5bfa38caf7040">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c7208212-5067-493a-8683-cc3386cb0efe" xmlns:ns3="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="662986cd6941c04829d5352220b24469" ns2:_="" ns3:_="">
     <xsd:import namespace="c7208212-5067-493a-8683-cc3386cb0efe"/>
@@ -3496,62 +3494,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TeamsChannelId xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Self_Registration_Enabled xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Math_Settings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <FolderType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Owner xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Owner>
-    <Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Teachers>
-    <Students xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Students>
-    <Student_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </Student_Groups>
-    <LMS_Mappings xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <IsNotebookLocked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <NotebookType xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <CultureName xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <AppVersion xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Invited_Teachers xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <DefaultSectionNames xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Is_Collaboration_Space_Locked xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Teams_Channel_Section_Location xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Templates xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Has_Teacher_Only_SectionGroup xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-    <Distribution_Groups xmlns="c7208212-5067-493a-8683-cc3386cb0efe" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
   <ds:schemaRefs>
@@ -3561,6 +3503,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
+    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EAF2F9FC-3A71-42D2-842A-D0923E27A331}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3577,15 +3530,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b9cacb4e-8c24-4bf7-a627-1f291d6d2a9f"/>
-    <ds:schemaRef ds:uri="c7208212-5067-493a-8683-cc3386cb0efe"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>